--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136348888</v>
       </c>
       <c r="B3" t="n">
-        <v>89369</v>
+        <v>89371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136348888</v>
       </c>
       <c r="B3" t="n">
-        <v>89371</v>
+        <v>89373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136348888</v>
       </c>
       <c r="B3" t="n">
-        <v>89373</v>
+        <v>89375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136348888</v>
       </c>
       <c r="B3" t="n">
-        <v>89375</v>
+        <v>89377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37034-2026 artfynd.xlsx
+++ b/artfynd/A 37034-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136348888</v>
       </c>
       <c r="B3" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136348887</v>
       </c>
       <c r="B6" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136348922</v>
       </c>
       <c r="B7" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136348889</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136348920</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136348921</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136348923</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
